--- a/编辑器/装备创建.xlsx
+++ b/编辑器/装备创建.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,11 @@
           <t>美术动画</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>修正</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -466,7 +471,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>基础铁剑。</t>
+          <t>锋利的铁剑：攻击伤害+20%，但防御卡格挡-2（攻强守弱）。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[{"type": "attack_damage_pct", "value": 20}, {"type": "defend_bonus", "value": -2}]</t>
         </is>
       </c>
     </row>
@@ -483,7 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>基础头盔，防御+1。</t>
+          <t>铁制头盔：回合开始获得 3 格挡，但每回合费用-1（稳守而沉重）。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[{"type": "block_on_turn_start", "value": 3}, {"type": "energy_modifier", "value": -1}]</t>
         </is>
       </c>
     </row>
@@ -500,7 +515,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>基础皮甲，防御+2。</t>
+          <t>厚实皮甲：生命上限+20，但移动力-1（耐打而笨重）。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[{"type": "max_hp", "value": 20}, {"type": "move_points", "value": -1}]</t>
         </is>
       </c>
     </row>
@@ -517,7 +537,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>轻便草鞋。</t>
+          <t>轻便草鞋：敏捷+2，但生命上限-10（轻装而脆）。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[{"type": "stat", "stat": "敏捷", "value": 2}, {"type": "max_hp", "value": -10}]</t>
         </is>
       </c>
     </row>
@@ -534,7 +559,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>朴素铜戒。</t>
+          <t>朴素铜戒：每回合抽牌+1，但意志力-2（更灵活，荷载容量下降）。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[{"type": "draw_modifier", "value": 1}, {"type": "stat", "stat": "意志力", "value": -2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>长枪</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>右手武器</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>杆部修长的长枪：攻击范围+1，但攻击伤害-15%（刺击够远，力道稍逊）。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[{"type": "attack_range", "value": 1}, {"type": "attack_damage_pct", "value": -15}]</t>
         </is>
       </c>
     </row>
